--- a/reports/Debug-snowbowl-20251216/For Winter Ending (Prior Year)_Revenue.xlsx
+++ b/reports/Debug-snowbowl-20251216/For Winter Ending (Prior Year)_Revenue.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="26">
   <si>
     <t>DepartmentTitle</t>
   </si>
@@ -31,9 +31,6 @@
     <t>Tickets</t>
   </si>
   <si>
-    <t xml:space="preserve">                         </t>
-  </si>
-  <si>
     <t xml:space="preserve">D1500                    </t>
   </si>
   <si>
@@ -43,10 +40,10 @@
     <t xml:space="preserve">T104                     </t>
   </si>
   <si>
+    <t xml:space="preserve">T100                     </t>
+  </si>
+  <si>
     <t xml:space="preserve">T103                     </t>
-  </si>
-  <si>
-    <t xml:space="preserve">T100                     </t>
   </si>
   <si>
     <t>Ski School</t>
@@ -483,11 +480,9 @@
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="2"/>
+      <c r="C2" s="2" t="s">
         <v>5</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>6</v>
       </c>
       <c r="D2" s="2">
         <v>-2002.5600</v>
@@ -498,10 +493,10 @@
         <v>4</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D3" s="2">
         <v>439.4500</v>
@@ -512,10 +507,10 @@
         <v>4</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D4" s="2">
         <v>-607.1000</v>
@@ -526,13 +521,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D5" s="2">
-        <v>106347.7700</v>
+        <v>1132353.5200</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -540,22 +535,22 @@
         <v>4</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D6" s="2">
-        <v>1132353.5200</v>
+        <v>106347.7700</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D7" s="2">
         <v>79163.3900</v>
@@ -563,11 +558,11 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D8" s="2">
         <v>470153.6100</v>
@@ -575,11 +570,11 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D9" s="2">
         <v>213287.9100</v>
@@ -587,11 +582,11 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D10" s="2">
         <v>5.0000</v>
@@ -599,11 +594,11 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D11" s="2">
         <v>244694.3000</v>
@@ -611,11 +606,11 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D12" s="2">
         <v>243733.0200</v>
@@ -623,11 +618,11 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D13" s="2">
         <v>34303.6400</v>
@@ -635,11 +630,11 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D14" s="2">
         <v>42.0000</v>
